--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_006.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_006.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="158">
   <si>
     <t>Sezione</t>
   </si>
@@ -369,6 +369,12 @@
   </si>
   <si>
     <t>flagFirmatario</t>
+  </si>
+  <si>
+    <t>Età(anni)</t>
+  </si>
+  <si>
+    <t>anni</t>
   </si>
   <si>
     <t>Provincia AIRE</t>
@@ -538,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.71875" customWidth="true" bestFit="true"/>
@@ -1340,7 +1346,7 @@
         <v>76</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>64</v>
@@ -1955,19 +1961,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -1978,19 +1984,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2001,19 +2007,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2024,19 +2030,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2047,19 +2053,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2070,19 +2076,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2093,19 +2099,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2116,19 +2122,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
@@ -2139,19 +2145,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2162,19 +2168,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2185,19 +2191,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2208,19 +2214,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2231,19 +2237,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2254,19 +2260,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2277,19 +2283,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2300,19 +2306,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2323,19 +2329,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2346,19 +2352,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2369,19 +2375,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2392,19 +2398,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
@@ -2415,19 +2421,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -2438,19 +2444,19 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
@@ -2461,19 +2467,19 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
@@ -2484,19 +2490,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
@@ -2507,19 +2513,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
@@ -2530,19 +2536,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -2553,19 +2559,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
@@ -2576,19 +2582,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2599,19 +2605,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
@@ -2622,19 +2628,19 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
@@ -2645,19 +2651,19 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
@@ -2668,19 +2674,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
@@ -2691,19 +2697,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
@@ -2717,19 +2723,19 @@
         <v>131</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="E95" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>29</v>
@@ -2740,16 +2746,16 @@
         <v>131</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
@@ -2760,22 +2766,22 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>29</v>
@@ -2783,19 +2789,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2806,22 +2812,22 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>29</v>
@@ -2829,19 +2835,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2852,19 +2858,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>22</v>
@@ -2875,22 +2881,22 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>29</v>
@@ -2898,22 +2904,22 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>29</v>
@@ -2921,22 +2927,22 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>29</v>
@@ -2944,19 +2950,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -2967,22 +2973,22 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>29</v>
@@ -2990,19 +2996,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -3013,19 +3019,19 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>22</v>
@@ -3036,22 +3042,22 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>29</v>
@@ -3059,22 +3065,22 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>29</v>
@@ -3082,22 +3088,22 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>29</v>
@@ -3105,22 +3111,22 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>29</v>
@@ -3128,22 +3134,22 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>29</v>
@@ -3151,22 +3157,22 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>29</v>
@@ -3174,19 +3180,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>22</v>
@@ -3197,19 +3203,19 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3220,19 +3226,19 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>22</v>
@@ -3243,19 +3249,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
@@ -3266,19 +3272,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>22</v>
@@ -3289,22 +3295,22 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>29</v>
@@ -3312,22 +3318,22 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>29</v>
@@ -3335,22 +3341,22 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>29</v>
@@ -3358,22 +3364,22 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="E123" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>29</v>
@@ -3381,19 +3387,19 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -3404,22 +3410,22 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>29</v>
@@ -3427,19 +3433,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
@@ -3450,19 +3456,19 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
@@ -3473,19 +3479,19 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
@@ -3496,19 +3502,19 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>10</v>
@@ -3519,19 +3525,19 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
@@ -3542,19 +3548,19 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
@@ -3565,19 +3571,19 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
@@ -3588,24 +3594,70 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E133" s="2" t="s">
+      <c r="C135" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F133" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G133" s="2" t="s">
+      <c r="F135" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G135" s="2" t="s">
         <v>29</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_006.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_006.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="162">
   <si>
     <t>Sezione</t>
   </si>
@@ -125,10 +125,22 @@
     <t>Dati generali</t>
   </si>
   <si>
+    <t>Formato Data Evento Matrimonio</t>
+  </si>
+  <si>
+    <t>evento.datiEventoMatrimonio</t>
+  </si>
+  <si>
+    <t>idFormatoDataEvento</t>
+  </si>
+  <si>
+    <t>Formato Data Evento Matrimonio - Descrizione</t>
+  </si>
+  <si>
+    <t>formatoDataEvento</t>
+  </si>
+  <si>
     <t>Data Evento Matrimonio</t>
-  </si>
-  <si>
-    <t>evento.datiEventoMatrimonio</t>
   </si>
   <si>
     <t>dataEvento</t>
@@ -544,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.71875" customWidth="true" bestFit="true"/>
@@ -955,7 +967,7 @@
         <v>37</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>38</v>
@@ -978,13 +990,13 @@
         <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
@@ -998,16 +1010,16 @@
         <v>36</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -1021,13 +1033,13 @@
         <v>36</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>46</v>
@@ -1050,7 +1062,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>48</v>
@@ -1073,7 +1085,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>50</v>
@@ -1096,7 +1108,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>52</v>
@@ -1119,7 +1131,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>54</v>
@@ -1139,13 +1151,13 @@
         <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>10</v>
@@ -1159,16 +1171,16 @@
         <v>36</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -1182,13 +1194,13 @@
         <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>61</v>
@@ -1202,19 +1214,19 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>10</v>
@@ -1225,19 +1237,19 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
@@ -1248,16 +1260,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>69</v>
@@ -1271,7 +1283,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>70</v>
@@ -1280,7 +1292,7 @@
         <v>23</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>71</v>
@@ -1294,7 +1306,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>72</v>
@@ -1303,7 +1315,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>73</v>
@@ -1317,16 +1329,16 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>75</v>
@@ -1340,7 +1352,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>76</v>
@@ -1349,7 +1361,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>77</v>
@@ -1363,7 +1375,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>78</v>
@@ -1372,7 +1384,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>79</v>
@@ -1386,7 +1398,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>80</v>
@@ -1395,7 +1407,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>81</v>
@@ -1409,7 +1421,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>82</v>
@@ -1418,7 +1430,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>83</v>
@@ -1432,7 +1444,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>84</v>
@@ -1441,7 +1453,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>85</v>
@@ -1455,7 +1467,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>86</v>
@@ -1464,7 +1476,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>87</v>
@@ -1478,7 +1490,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>88</v>
@@ -1487,7 +1499,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>89</v>
@@ -1501,19 +1513,19 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -1524,19 +1536,19 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -1547,16 +1559,16 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>94</v>
@@ -1570,7 +1582,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>95</v>
@@ -1579,7 +1591,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>96</v>
@@ -1593,7 +1605,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>97</v>
@@ -1602,7 +1614,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>98</v>
@@ -1616,7 +1628,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>99</v>
@@ -1625,7 +1637,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>100</v>
@@ -1639,7 +1651,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>101</v>
@@ -1648,7 +1660,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>102</v>
@@ -1662,7 +1674,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>103</v>
@@ -1671,7 +1683,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>104</v>
@@ -1685,7 +1697,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>105</v>
@@ -1694,7 +1706,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>106</v>
@@ -1708,7 +1720,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>107</v>
@@ -1717,7 +1729,7 @@
         <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>108</v>
@@ -1731,7 +1743,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>109</v>
@@ -1740,7 +1752,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>110</v>
@@ -1754,7 +1766,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>111</v>
@@ -1763,7 +1775,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>112</v>
@@ -1777,16 +1789,16 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>114</v>
@@ -1800,16 +1812,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>116</v>
@@ -1823,7 +1835,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>117</v>
@@ -1832,7 +1844,7 @@
         <v>23</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>118</v>
@@ -1846,16 +1858,16 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>120</v>
@@ -1869,16 +1881,16 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>122</v>
@@ -1892,7 +1904,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>123</v>
@@ -1901,7 +1913,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>124</v>
@@ -1915,7 +1927,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>125</v>
@@ -1924,7 +1936,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>126</v>
@@ -1938,7 +1950,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>127</v>
@@ -1947,7 +1959,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>128</v>
@@ -1961,7 +1973,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>129</v>
@@ -1970,7 +1982,7 @@
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>130</v>
@@ -1984,19 +1996,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2007,19 +2019,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>131</v>
+        <v>66</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2030,16 +2042,16 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>69</v>
@@ -2053,7 +2065,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>70</v>
@@ -2062,7 +2074,7 @@
         <v>23</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>71</v>
@@ -2076,7 +2088,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>72</v>
@@ -2085,7 +2097,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>73</v>
@@ -2099,16 +2111,16 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>75</v>
@@ -2122,7 +2134,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>76</v>
@@ -2131,7 +2143,7 @@
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>77</v>
@@ -2145,7 +2157,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>78</v>
@@ -2154,7 +2166,7 @@
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>79</v>
@@ -2168,7 +2180,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>80</v>
@@ -2177,7 +2189,7 @@
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>81</v>
@@ -2191,7 +2203,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>82</v>
@@ -2200,7 +2212,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>83</v>
@@ -2214,7 +2226,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>84</v>
@@ -2223,7 +2235,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>85</v>
@@ -2237,7 +2249,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>86</v>
@@ -2246,7 +2258,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>87</v>
@@ -2260,7 +2272,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>88</v>
@@ -2269,7 +2281,7 @@
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>89</v>
@@ -2283,19 +2295,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2306,19 +2318,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2329,16 +2341,16 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>94</v>
@@ -2352,7 +2364,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>95</v>
@@ -2361,7 +2373,7 @@
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>96</v>
@@ -2375,7 +2387,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>97</v>
@@ -2384,7 +2396,7 @@
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>98</v>
@@ -2398,7 +2410,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>99</v>
@@ -2407,7 +2419,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>100</v>
@@ -2421,7 +2433,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>101</v>
@@ -2430,7 +2442,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>102</v>
@@ -2444,7 +2456,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>103</v>
@@ -2453,7 +2465,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>104</v>
@@ -2467,7 +2479,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>105</v>
@@ -2476,7 +2488,7 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>106</v>
@@ -2490,7 +2502,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>107</v>
@@ -2499,7 +2511,7 @@
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>108</v>
@@ -2513,7 +2525,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>109</v>
@@ -2522,7 +2534,7 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>110</v>
@@ -2536,7 +2548,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>111</v>
@@ -2545,7 +2557,7 @@
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>112</v>
@@ -2559,16 +2571,16 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>114</v>
@@ -2582,16 +2594,16 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>116</v>
@@ -2605,7 +2617,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>117</v>
@@ -2614,7 +2626,7 @@
         <v>23</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>118</v>
@@ -2628,16 +2640,16 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>120</v>
@@ -2651,16 +2663,16 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>122</v>
@@ -2674,7 +2686,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>123</v>
@@ -2683,7 +2695,7 @@
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>124</v>
@@ -2697,7 +2709,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>125</v>
@@ -2706,7 +2718,7 @@
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>126</v>
@@ -2720,7 +2732,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>127</v>
@@ -2729,7 +2741,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>128</v>
@@ -2743,7 +2755,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>129</v>
@@ -2752,7 +2764,7 @@
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>130</v>
@@ -2766,22 +2778,22 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>29</v>
@@ -2789,19 +2801,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C98" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2812,22 +2824,22 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>67</v>
+        <v>140</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>29</v>
@@ -2835,16 +2847,16 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>69</v>
@@ -2858,22 +2870,22 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>71</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>29</v>
@@ -2881,7 +2893,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>72</v>
@@ -2890,7 +2902,7 @@
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>73</v>
@@ -2904,7 +2916,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>74</v>
@@ -2913,7 +2925,7 @@
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>75</v>
@@ -2927,7 +2939,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>76</v>
@@ -2936,13 +2948,13 @@
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>77</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>29</v>
@@ -2950,22 +2962,22 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>29</v>
@@ -2973,22 +2985,22 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>81</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>29</v>
@@ -2996,16 +3008,16 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>83</v>
@@ -3019,22 +3031,22 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>29</v>
@@ -3042,7 +3054,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>86</v>
@@ -3051,7 +3063,7 @@
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>87</v>
@@ -3065,7 +3077,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>88</v>
@@ -3074,7 +3086,7 @@
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>89</v>
@@ -3088,22 +3100,22 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>29</v>
@@ -3111,22 +3123,22 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>29</v>
@@ -3134,22 +3146,22 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>94</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>29</v>
@@ -3157,22 +3169,22 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>29</v>
@@ -3180,22 +3192,22 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>29</v>
@@ -3203,7 +3215,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>99</v>
@@ -3212,13 +3224,13 @@
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>29</v>
@@ -3226,7 +3238,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>101</v>
@@ -3235,7 +3247,7 @@
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>102</v>
@@ -3249,7 +3261,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>103</v>
@@ -3258,7 +3270,7 @@
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>104</v>
@@ -3272,7 +3284,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>105</v>
@@ -3281,7 +3293,7 @@
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>106</v>
@@ -3295,7 +3307,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>107</v>
@@ -3304,7 +3316,7 @@
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>108</v>
@@ -3318,7 +3330,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>109</v>
@@ -3327,7 +3339,7 @@
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>110</v>
@@ -3341,7 +3353,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>111</v>
@@ -3350,13 +3362,13 @@
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>112</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>29</v>
@@ -3364,22 +3376,22 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>114</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>29</v>
@@ -3387,22 +3399,22 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>116</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>29</v>
@@ -3410,22 +3422,22 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>29</v>
@@ -3433,19 +3445,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
@@ -3456,22 +3468,22 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>29</v>
@@ -3479,16 +3491,16 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>145</v>
@@ -3502,7 +3514,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>146</v>
@@ -3511,7 +3523,7 @@
         <v>23</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>147</v>
@@ -3525,7 +3537,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>148</v>
@@ -3534,7 +3546,7 @@
         <v>23</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>149</v>
@@ -3548,16 +3560,16 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>151</v>
@@ -3571,16 +3583,16 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>153</v>
@@ -3594,7 +3606,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>154</v>
@@ -3603,7 +3615,7 @@
         <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>155</v>
@@ -3617,7 +3629,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>156</v>
@@ -3626,7 +3638,7 @@
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>157</v>
@@ -3640,24 +3652,70 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G137" s="2" t="s">
         <v>29</v>
       </c>
     </row>
